--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488030_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488030_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5215</v>
+        <v>3.6981</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0138</v>
+        <v>3.7445</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4922</v>
+        <v>-0.0464</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7039</v>
+        <v>1.3526</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2742</v>
+        <v>-0.3406</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5703</v>
+        <v>1.6932</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5406</v>
+        <v>2.0574</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4603</v>
+        <v>0.1211</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0804</v>
+        <v>1.9363</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8367</v>
+        <v>-0.7048</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1861</v>
+        <v>-0.4617</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6506</v>
+        <v>-0.2431</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3943</v>
+        <v>0.8103</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4465</v>
+        <v>0.48</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0523</v>
+        <v>0.3303</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4234</v>
+        <v>0.9405</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0178</v>
+        <v>1.2071</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5944</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1969</v>
+        <v>2.979</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5803</v>
+        <v>4.5274</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3834</v>
+        <v>-1.5484</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3526</v>
+        <v>0.7039</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3406</v>
+        <v>1.2742</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6932</v>
+        <v>-0.5703</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0574</v>
+        <v>1.5406</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1211</v>
+        <v>1.4603</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9363</v>
+        <v>0.0804</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7048</v>
+        <v>-0.8367</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4617</v>
+        <v>-0.1861</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2431</v>
+        <v>-0.6506</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3091</v>
+        <v>0.8517</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3158</v>
+        <v>0.9601</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0067</v>
+        <v>-0.1084</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9405</v>
+        <v>1.4234</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>3.0178</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2666</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0501</v>
+        <v>2.3713</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4882</v>
+        <v>3.8375</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4381</v>
+        <v>-1.4661</v>
       </c>
       <c r="G4" t="n">
         <v>1.708</v>
@@ -766,13 +766,13 @@
         <v>0.7929</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5157</v>
+        <v>0.8369</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3107</v>
+        <v>0.66</v>
       </c>
       <c r="U4" t="n">
-        <v>0.205</v>
+        <v>0.1769</v>
       </c>
       <c r="V4" t="n">
         <v>2.0068</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1767</v>
+        <v>1.0136</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5307</v>
+        <v>1.4517</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3539</v>
+        <v>-0.4381</v>
       </c>
       <c r="G5" t="n">
         <v>1.1614</v>
@@ -844,13 +844,13 @@
         <v>0.3964</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5899</v>
+        <v>0.4267</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3782</v>
+        <v>0.2992</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2117</v>
+        <v>0.1275</v>
       </c>
       <c r="V5" t="n">
         <v>0.0201</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8247</v>
+        <v>0.7073</v>
       </c>
       <c r="E6" t="n">
-        <v>0.699</v>
+        <v>0.722</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1257</v>
+        <v>-0.0147</v>
       </c>
       <c r="G6" t="n">
         <v>0.7241</v>
@@ -922,13 +922,13 @@
         <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2808</v>
+        <v>0.1633</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3158</v>
+        <v>0.3387</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.035</v>
+        <v>-0.1754</v>
       </c>
       <c r="V6" t="n">
         <v>0.2163</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3911</v>
+        <v>0.3027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0002</v>
+        <v>0.3027</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3913</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1877</v>
+        <v>0.3027</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4311</v>
+        <v>0.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2434</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8547</v>
+        <v>0.3027</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6319</v>
+        <v>0.3027</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4866</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0424</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7993</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2431</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3787</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2172</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3782</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.839</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3027</v>
+        <v>0.1769</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3027</v>
+        <v>-0.1021</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3027</v>
+        <v>-0.1877</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3027</v>
+        <v>-1.4311</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.2434</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3027</v>
+        <v>0.8547</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3027</v>
+        <v>-0.6319</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.4866</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.0424</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.7993</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.2431</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.003</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2763</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.7267</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2932</v>
+        <v>-0.7007</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7174</v>
+        <v>0.31</v>
       </c>
       <c r="F9" t="n">
         <v>-1.0107</v>
@@ -1156,10 +1156,10 @@
         <v>0.1982</v>
       </c>
       <c r="S9" t="n">
+        <v>-0.1982</v>
+      </c>
+      <c r="T9" t="n">
         <v>0.2093</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.6167</v>
       </c>
       <c r="U9" t="n">
         <v>-0.4075</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9649</v>
+        <v>-1.4202</v>
       </c>
       <c r="E10" t="n">
-        <v>0.009599999999999999</v>
+        <v>2.1966</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9745</v>
+        <v>-3.6169</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4663</v>
+        <v>0.8744</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1664</v>
+        <v>2.9444</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7000999999999999</v>
+        <v>-2.0701</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3216</v>
+        <v>3.1161</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0404</v>
+        <v>3.8678</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2812</v>
+        <v>-0.7517</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7879</v>
+        <v>-2.2417</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2067</v>
+        <v>-0.9233</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4189</v>
+        <v>-1.3184</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2827</v>
+        <v>-0.7002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.312</v>
+        <v>0.0717</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0293</v>
+        <v>-0.7719</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8107</v>
+        <v>-1.5944</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8107</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>J. CEBRIAN ROSAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1219</v>
+        <v>-1.5699</v>
       </c>
       <c r="E11" t="n">
-        <v>1.523</v>
+        <v>-0.2853</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.645</v>
+        <v>-1.2846</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8744</v>
+        <v>-0.2223</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9444</v>
+        <v>1.2736</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0701</v>
+        <v>-1.4959</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1161</v>
+        <v>1.4839</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8678</v>
+        <v>1.6615</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7517</v>
+        <v>-0.1775</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2417</v>
+        <v>-1.7062</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9233</v>
+        <v>-0.3879</v>
       </c>
       <c r="O11" t="n">
         <v>-1.3184</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4019</v>
+        <v>0.245</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6019</v>
+        <v>0.213</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8</v>
+        <v>0.032</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5944</v>
+        <v>-0.7997</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5944</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. CEBRIAN ROSAS</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4129</v>
+        <v>-1.8631</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1002</v>
+        <v>0.1115</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3127</v>
+        <v>-1.9745</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2223</v>
+        <v>-0.4663</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2736</v>
+        <v>-1.1664</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4959</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4839</v>
+        <v>0.3216</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6615</v>
+        <v>0.0404</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1775</v>
+        <v>0.2812</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7062</v>
+        <v>-0.7879</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3879</v>
+        <v>-1.2067</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3184</v>
+        <v>0.4189</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.598</v>
+        <v>-0.1808</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6019</v>
+        <v>-0.2101</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0039</v>
+        <v>0.0293</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7997</v>
+        <v>-1.8107</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7997</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.9138</v>
+        <v>-7.314</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2887</v>
+        <v>-3.717</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.625</v>
+        <v>-3.597</v>
       </c>
       <c r="G13" t="n">
         <v>-4.892</v>
@@ -1468,13 +1468,13 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3064</v>
+        <v>-0.7066</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6019</v>
+        <v>-0.0302</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7045</v>
+        <v>-0.6765</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7243000000000001</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.243</v>
+        <v>-1.618999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4756</v>
+        <v>13.0995</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.7185</v>
+        <v>-14.7184</v>
       </c>
       <c r="G14" t="n">
         <v>0.3580999999999985</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3298000000000005</v>
+        <v>0.3297999999999996</v>
       </c>
       <c r="I14" t="n">
         <v>0.02849999999999997</v>
@@ -1531,13 +1531,13 @@
         <v>-12.0925</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.944600000000001</v>
+        <v>-6.9446</v>
       </c>
       <c r="O14" t="n">
         <v>-5.1478</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.9467</v>
+        <v>-5.946700000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.8754</v>
@@ -1546,13 +1546,13 @@
         <v>7.928900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9273</v>
+        <v>2.5511</v>
       </c>
       <c r="T14" t="n">
-        <v>2.644199999999999</v>
+        <v>3.268</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7171000000000001</v>
+        <v>-0.717</v>
       </c>
       <c r="V14" t="n">
         <v>1.4183</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2859</v>
+        <v>7.8361</v>
       </c>
       <c r="E15" t="n">
-        <v>7.9339</v>
+        <v>9.1564</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6481</v>
+        <v>-1.3202</v>
       </c>
       <c r="G15" t="n">
         <v>6.8513</v>
@@ -1624,13 +1624,13 @@
         <v>2.5769</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6328</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1121</v>
+        <v>0.1103</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.1929</v>
       </c>
       <c r="V15" t="n">
         <v>0.6709000000000001</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.173</v>
+        <v>3.007</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9288</v>
+        <v>4.5191</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7559</v>
+        <v>-1.5121</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0328</v>
+        <v>1.2529</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6279</v>
+        <v>-1.4468</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5952</v>
+        <v>2.6997</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7408</v>
+        <v>1.1406</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4193</v>
+        <v>-1.1288</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3214</v>
+        <v>2.2694</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.708</v>
+        <v>0.1123</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7914</v>
+        <v>-0.318</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9166</v>
+        <v>0.4303</v>
       </c>
       <c r="P16" t="n">
         <v>1.3876</v>
@@ -1702,22 +1702,22 @@
         <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6227</v>
+        <v>-0.234</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7827</v>
+        <v>0.0259</v>
       </c>
       <c r="U16" t="n">
-        <v>0.84</v>
+        <v>-0.2598</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8701</v>
+        <v>0.6005</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6036</v>
+        <v>3.5509</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4737</v>
+        <v>-2.9504</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9242</v>
+        <v>2.2823</v>
       </c>
       <c r="E17" t="n">
-        <v>5.2155</v>
+        <v>3.993</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2912</v>
+        <v>-1.7107</v>
       </c>
       <c r="G17" t="n">
         <v>0.5179</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1605</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9164</v>
+        <v>0.694</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7559</v>
+        <v>-0.1754</v>
       </c>
       <c r="V17" t="n">
         <v>-0.34</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9227</v>
+        <v>2.225</v>
       </c>
       <c r="E18" t="n">
-        <v>4.9266</v>
+        <v>3.2989</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0038</v>
+        <v>-1.0739</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2529</v>
+        <v>0.0328</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4468</v>
+        <v>0.6279</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6997</v>
+        <v>-0.5952</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1406</v>
+        <v>1.7408</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1288</v>
+        <v>1.4193</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2694</v>
+        <v>0.3214</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1123</v>
+        <v>-1.708</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.318</v>
+        <v>-0.7914</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4303</v>
+        <v>-0.9166</v>
       </c>
       <c r="P18" t="n">
         <v>1.3876</v>
@@ -1858,28 +1858,28 @@
         <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3182</v>
+        <v>1.6748</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4333</v>
+        <v>1.1528</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7516</v>
+        <v>0.522</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6005</v>
+        <v>-0.8701</v>
       </c>
       <c r="W18" t="n">
-        <v>3.5509</v>
+        <v>0.6036</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.9504</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3025</v>
+        <v>0.8104</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1821</v>
+        <v>2.3831</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1204</v>
+        <v>-1.5726</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1142</v>
+        <v>0.5788</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1575</v>
+        <v>1.9371</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2717</v>
+        <v>-1.3583</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0404</v>
+        <v>2.8436</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0404</v>
+        <v>2.8721</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.0285</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0738</v>
+        <v>-2.2648</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1979</v>
+        <v>-0.9351</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2717</v>
+        <v>-1.3298</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0192</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1248</v>
+        <v>-0.2623</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0466</v>
+        <v>0.2431</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2666</v>
+        <v>-1.1367</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.115</v>
+        <v>0.3541</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7718</v>
+        <v>0.1821</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6569</v>
+        <v>0.172</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5788</v>
+        <v>0.1142</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9371</v>
+        <v>-0.1575</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3583</v>
+        <v>0.2717</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8436</v>
+        <v>0.0404</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8721</v>
+        <v>0.0404</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0285</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2648</v>
+        <v>0.0738</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9351</v>
+        <v>-0.1979</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3298</v>
+        <v>0.2717</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7147</v>
+        <v>-0.0266</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8736</v>
+        <v>-0.1248</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1589</v>
+        <v>0.0982</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1367</v>
+        <v>0.2666</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. PANOS HUERTAS</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0036</v>
+        <v>0.1778</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1.1756</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0036</v>
+        <v>-0.9979</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2057</v>
+        <v>-0.6122</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.066</v>
+        <v>-0.7441</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2717</v>
+        <v>0.1319</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7678</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2057</v>
+        <v>-1.38</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.066</v>
+        <v>-0.8652</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2717</v>
+        <v>-0.5148</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2093</v>
+        <v>-0.6837</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.3413</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2093</v>
+        <v>-0.3424</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>L. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5059</v>
+        <v>0.1323</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7682</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2741</v>
+        <v>0.1323</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6122</v>
+        <v>0.2057</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7441</v>
+        <v>-0.066</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1319</v>
+        <v>0.2717</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7678</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1211</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6467000000000001</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.38</v>
+        <v>0.2057</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8652</v>
+        <v>-0.066</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5148</v>
+        <v>0.2717</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3674</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7488</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6186</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3643</v>
+        <v>-3.5095</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0742</v>
+        <v>-3.463</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2901</v>
+        <v>-0.0465</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9835</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2301</v>
+        <v>-0.3753</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9873</v>
+        <v>-0.3761</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2428</v>
+        <v>0.0008</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5471</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.6065</v>
+        <v>-9.0351</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9343</v>
+        <v>-6.5268</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6722</v>
+        <v>-2.5083</v>
       </c>
       <c r="G24" t="n">
         <v>-7.3161</v>
@@ -2326,13 +2326,13 @@
         <v>2.5769</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1596</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5688</v>
+        <v>-0.1613</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5908</v>
+        <v>-0.4269</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5362</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.242999999999999</v>
+        <v>4.2804</v>
       </c>
       <c r="E25" t="n">
         <v>14.7184</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.4755</v>
+        <v>-10.4379</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3582000000000001</v>
+        <v>-0.3581999999999983</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3297999999999996</v>
+        <v>-0.3298000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.02859999999999907</v>
+        <v>-0.02859999999999996</v>
       </c>
       <c r="J25" t="n">
         <v>12.0926</v>
       </c>
       <c r="K25" t="n">
-        <v>6.944499999999999</v>
+        <v>6.944500000000001</v>
       </c>
       <c r="L25" t="n">
         <v>5.147899999999999</v>
@@ -2404,13 +2404,13 @@
         <v>13.8757</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.9271</v>
+        <v>0.1104000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7170000000000005</v>
+        <v>0.7172000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.644200000000001</v>
+        <v>-0.6067</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4184</v>
